--- a/document/webエンジニアスキル状況機能・非機能要件.xlsx
+++ b/document/webエンジニアスキル状況機能・非機能要件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/317e370d51a78cda/Desktop/WEBスクール/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="11_AD4D066CA252ABDACC10488BE9D5EBD472EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D25ED1F-6F01-4370-AD5A-FCDE28BDDF9A}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="11_AD4D066CA252ABDACC10488BE9D5EBD472EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6149AC04-76A7-436D-8C50-4D3B0436DD14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,26 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>【機能】</t>
     <phoneticPr fontId="1"/>
@@ -124,10 +133,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>windows11</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Google Chrome</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -236,6 +241,43 @@
   </si>
   <si>
     <t>○セキュリティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セキュリティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対策方法</t>
+    <rPh sb="0" eb="4">
+      <t>タイサクホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">XSS </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サニタイジング（スクリプト無害化）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSRF </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワンタイムトークン</t>
+  </si>
+  <si>
+    <t>SQLインジェクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレースホルダ変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Linux 6.18/macOS 15/windows11</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -273,7 +315,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -296,13 +338,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -311,6 +389,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,8 +686,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:BH18"/>
+  <dimension ref="C4:BH23"/>
   <sheetFormatPr defaultColWidth="2.69921875" defaultRowHeight="18"/>
+  <cols>
+    <col min="43" max="43" width="2.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="4" spans="3:60">
       <c r="C4" t="s">
@@ -608,478 +701,616 @@
       </c>
     </row>
     <row r="6" spans="3:60">
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="s">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
       <c r="AD6" t="s">
         <v>17</v>
       </c>
-      <c r="AJ6" s="4" t="s">
+      <c r="AJ6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AK6" s="4"/>
-      <c r="AL6" s="4"/>
-      <c r="AM6" s="4"/>
-      <c r="AN6" s="2" t="s">
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2" t="s">
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+    </row>
+    <row r="7" spans="3:60">
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-    </row>
-    <row r="7" spans="3:60">
-      <c r="D7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+    </row>
+    <row r="8" spans="3:60">
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+    </row>
+    <row r="9" spans="3:60">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="AJ7" s="4"/>
-      <c r="AK7" s="4"/>
-      <c r="AL7" s="4"/>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+    </row>
+    <row r="10" spans="3:60">
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="AD10" t="s">
         <v>22</v>
       </c>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-    </row>
-    <row r="8" spans="3:60">
-      <c r="D8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
+    </row>
+    <row r="11" spans="3:60">
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="3:60">
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="s">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="AJ11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK11" s="2"/>
+      <c r="AL11" s="2"/>
+      <c r="AM11" s="2"/>
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="AP11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="2"/>
+      <c r="AS11" s="2"/>
+      <c r="AT11" s="2"/>
+      <c r="AU11" s="2"/>
+      <c r="AV11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW11" s="2"/>
+      <c r="AX11" s="2"/>
+      <c r="AY11" s="2"/>
+      <c r="AZ11" s="2"/>
+      <c r="BA11" s="2"/>
+      <c r="BB11" s="2"/>
+      <c r="BC11" s="2"/>
+      <c r="BD11" s="2"/>
+      <c r="BE11" s="2"/>
+      <c r="BF11" s="2"/>
+      <c r="BG11" s="2"/>
+      <c r="BH11" s="2"/>
+    </row>
+    <row r="12" spans="3:60">
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="3:60">
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="AJ12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="1"/>
+      <c r="AP12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ12" s="1"/>
+      <c r="AR12" s="1"/>
+      <c r="AS12" s="1"/>
+      <c r="AT12" s="1"/>
+      <c r="AU12" s="1"/>
+      <c r="AV12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AW12" s="1"/>
+      <c r="AX12" s="1"/>
+      <c r="AY12" s="1"/>
+      <c r="AZ12" s="1"/>
+      <c r="BA12" s="1"/>
+      <c r="BB12" s="1"/>
+      <c r="BC12" s="1"/>
+      <c r="BD12" s="1"/>
+      <c r="BE12" s="1"/>
+      <c r="BF12" s="1"/>
+      <c r="BG12" s="1"/>
+      <c r="BH12" s="1"/>
+    </row>
+    <row r="13" spans="3:60">
+      <c r="D13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="AD10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="3:60">
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="s">
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="AJ13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+      <c r="AO13" s="1"/>
+      <c r="AP13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ13" s="1"/>
+      <c r="AR13" s="1"/>
+      <c r="AS13" s="1"/>
+      <c r="AT13" s="1"/>
+      <c r="AU13" s="1"/>
+      <c r="AV13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW13" s="1"/>
+      <c r="AX13" s="1"/>
+      <c r="AY13" s="1"/>
+      <c r="AZ13" s="1"/>
+      <c r="BA13" s="1"/>
+      <c r="BB13" s="1"/>
+      <c r="BC13" s="1"/>
+      <c r="BD13" s="1"/>
+      <c r="BE13" s="1"/>
+      <c r="BF13" s="1"/>
+      <c r="BG13" s="1"/>
+      <c r="BH13" s="1"/>
+    </row>
+    <row r="14" spans="3:60">
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="AJ11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="3"/>
-      <c r="AS11" s="3"/>
-      <c r="AT11" s="3"/>
-      <c r="AU11" s="3"/>
-      <c r="AV11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AW11" s="3"/>
-      <c r="AX11" s="3"/>
-      <c r="AY11" s="3"/>
-      <c r="AZ11" s="3"/>
-      <c r="BA11" s="3"/>
-      <c r="BB11" s="3"/>
-      <c r="BC11" s="3"/>
-      <c r="BD11" s="3"/>
-      <c r="BE11" s="3"/>
-      <c r="BF11" s="3"/>
-      <c r="BG11" s="3"/>
-      <c r="BH11" s="3"/>
-    </row>
-    <row r="12" spans="3:60">
-      <c r="D12" s="2" t="s">
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="AJ14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ14" s="1"/>
+      <c r="AR14" s="1"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="1"/>
+      <c r="AU14" s="1"/>
+      <c r="AV14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="1"/>
+      <c r="AZ14" s="1"/>
+      <c r="BA14" s="1"/>
+      <c r="BB14" s="1"/>
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1"/>
+      <c r="BE14" s="1"/>
+      <c r="BF14" s="1"/>
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="1"/>
+    </row>
+    <row r="15" spans="3:60">
+      <c r="AJ15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+      <c r="AP15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="AJ12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="2"/>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
-      <c r="AP12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AQ12" s="2"/>
-      <c r="AR12" s="2"/>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2" t="s">
+      <c r="AQ15" s="1"/>
+      <c r="AR15" s="1"/>
+      <c r="AS15" s="1"/>
+      <c r="AT15" s="1"/>
+      <c r="AU15" s="1"/>
+      <c r="AV15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW15" s="1"/>
+      <c r="AX15" s="1"/>
+      <c r="AY15" s="1"/>
+      <c r="AZ15" s="1"/>
+      <c r="BA15" s="1"/>
+      <c r="BB15" s="1"/>
+      <c r="BC15" s="1"/>
+      <c r="BD15" s="1"/>
+      <c r="BE15" s="1"/>
+      <c r="BF15" s="1"/>
+      <c r="BG15" s="1"/>
+      <c r="BH15" s="1"/>
+    </row>
+    <row r="18" spans="30:60">
+      <c r="AD18" t="s">
         <v>39</v>
       </c>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2"/>
-      <c r="BB12" s="2"/>
-      <c r="BC12" s="2"/>
-      <c r="BD12" s="2"/>
-      <c r="BE12" s="2"/>
-      <c r="BF12" s="2"/>
-      <c r="BG12" s="2"/>
-      <c r="BH12" s="2"/>
-    </row>
-    <row r="13" spans="3:60">
-      <c r="D13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="AJ13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
-      <c r="AP13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AQ13" s="2"/>
-      <c r="AR13" s="2"/>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="2"/>
-      <c r="BB13" s="2"/>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2"/>
-      <c r="BE13" s="2"/>
-      <c r="BF13" s="2"/>
-      <c r="BG13" s="2"/>
-      <c r="BH13" s="2"/>
-    </row>
-    <row r="14" spans="3:60">
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="AJ14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
-      <c r="AP14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2"/>
-      <c r="BA14" s="2"/>
-      <c r="BB14" s="2"/>
-      <c r="BC14" s="2"/>
-      <c r="BD14" s="2"/>
-      <c r="BE14" s="2"/>
-      <c r="BF14" s="2"/>
-      <c r="BG14" s="2"/>
-      <c r="BH14" s="2"/>
-    </row>
-    <row r="15" spans="3:60">
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="AJ15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK15" s="2"/>
-      <c r="AL15" s="2"/>
-      <c r="AM15" s="2"/>
-      <c r="AN15" s="2"/>
-      <c r="AO15" s="2"/>
-      <c r="AP15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AQ15" s="2"/>
-      <c r="AR15" s="2"/>
-      <c r="AS15" s="2"/>
-      <c r="AT15" s="2"/>
-      <c r="AU15" s="2"/>
-      <c r="AV15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW15" s="2"/>
-      <c r="AX15" s="2"/>
-      <c r="AY15" s="2"/>
-      <c r="AZ15" s="2"/>
-      <c r="BA15" s="2"/>
-      <c r="BB15" s="2"/>
-      <c r="BC15" s="2"/>
-      <c r="BD15" s="2"/>
-      <c r="BE15" s="2"/>
-      <c r="BF15" s="2"/>
-      <c r="BG15" s="2"/>
-      <c r="BH15" s="2"/>
-    </row>
-    <row r="18" spans="30:30">
-      <c r="AD18" t="s">
+    </row>
+    <row r="20" spans="30:60">
+      <c r="AJ20" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AK20" s="2"/>
+      <c r="AL20" s="2"/>
+      <c r="AM20" s="2"/>
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+      <c r="AT20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU20" s="6"/>
+      <c r="AV20" s="6"/>
+      <c r="AW20" s="6"/>
+      <c r="AX20" s="6"/>
+      <c r="AY20" s="6"/>
+      <c r="AZ20" s="6"/>
+      <c r="BA20" s="6"/>
+      <c r="BB20" s="6"/>
+      <c r="BC20" s="6"/>
+      <c r="BD20" s="6"/>
+      <c r="BE20" s="6"/>
+      <c r="BF20" s="6"/>
+      <c r="BG20" s="6"/>
+      <c r="BH20" s="7"/>
+    </row>
+    <row r="21" spans="30:60">
+      <c r="AJ21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK21" s="4"/>
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="4"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="4"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BH21" s="4"/>
+    </row>
+    <row r="22" spans="30:60">
+      <c r="AJ22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="4"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+    </row>
+    <row r="23" spans="30:60">
+      <c r="AJ23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BH23" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="AP15:AU15"/>
-    <mergeCell ref="AP13:AU13"/>
-    <mergeCell ref="AP14:AU14"/>
-    <mergeCell ref="AP11:AU11"/>
-    <mergeCell ref="AP12:AU12"/>
-    <mergeCell ref="AJ14:AO14"/>
-    <mergeCell ref="AJ15:AO15"/>
-    <mergeCell ref="AV11:BH11"/>
-    <mergeCell ref="AV15:BH15"/>
-    <mergeCell ref="AV12:BH12"/>
-    <mergeCell ref="AV13:BH13"/>
-    <mergeCell ref="AV14:BH14"/>
+  <mergeCells count="55">
+    <mergeCell ref="AJ22:AS22"/>
+    <mergeCell ref="AJ23:AS23"/>
+    <mergeCell ref="AT22:BH22"/>
+    <mergeCell ref="AT23:BH23"/>
+    <mergeCell ref="AQ6:BB6"/>
+    <mergeCell ref="AQ7:BB7"/>
+    <mergeCell ref="AJ20:AS20"/>
+    <mergeCell ref="AT20:BH20"/>
+    <mergeCell ref="AT21:BH21"/>
+    <mergeCell ref="AJ21:AS21"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="L6:Q6"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R11:W11"/>
+    <mergeCell ref="R12:W12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="D12:K12"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="AJ6:AM7"/>
     <mergeCell ref="AN6:AP6"/>
     <mergeCell ref="AN7:AP7"/>
-    <mergeCell ref="AQ6:AZ6"/>
-    <mergeCell ref="AQ7:AZ7"/>
     <mergeCell ref="AJ11:AO11"/>
     <mergeCell ref="AJ12:AO12"/>
     <mergeCell ref="AJ13:AO13"/>
@@ -1090,25 +1321,18 @@
     <mergeCell ref="R8:W8"/>
     <mergeCell ref="R9:W9"/>
     <mergeCell ref="R10:W10"/>
-    <mergeCell ref="R11:W11"/>
-    <mergeCell ref="R12:W12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="L6:Q6"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="AJ14:AO14"/>
+    <mergeCell ref="AJ15:AO15"/>
+    <mergeCell ref="AV11:BH11"/>
+    <mergeCell ref="AV15:BH15"/>
+    <mergeCell ref="AV12:BH12"/>
+    <mergeCell ref="AV13:BH13"/>
+    <mergeCell ref="AV14:BH14"/>
+    <mergeCell ref="AP15:AU15"/>
+    <mergeCell ref="AP13:AU13"/>
+    <mergeCell ref="AP14:AU14"/>
+    <mergeCell ref="AP11:AU11"/>
+    <mergeCell ref="AP12:AU12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
